--- a/pdf/03_香盤表_モデル用_当日.xlsx
+++ b/pdf/03_香盤表_モデル用_当日.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>難波遥さん　／　10月6日（火）　／　9:00〜15:10</t>
+          <t>難波遥さん　／　10月6日（火）　／　9:00〜15:45</t>
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -585,7 +585,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>10月6日（火）　9:00集合　　場所 ── BROOKLYN MUSEUM 表参道店（店休日）・表参道けやき並木 → 代官山</t>
+          <t>10月6日（火）　9:00集合　　場所 ── BROOKLYN MUSEUM 表参道店（店休日）・南青山 → 代官山（車で移動）</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -601,7 +601,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>9:00〜15:10　　出演 ── 難波遥さん（一日）</t>
+          <t>9:00〜15:45　　出演 ── 難波遥さん（一日）</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -676,7 +676,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 午 前 ── 店 舗 と 、 け や き 並 木</t>
+          <t xml:space="preserve"> 午 前 ── 店 舗 と 、 南 青 山</t>
         </is>
       </c>
       <c r="B11" s="12" t="n"/>
@@ -699,13 +699,13 @@
       <c r="C12" s="15" t="inlineStr">
         <is>
           <t>難波遥さん
-一色目の衣装・鞄</t>
+④の衣装 一そろい</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
           <t>支度
-着替えて、髪を整える。カメラを置く位置と、歩いてもらう道を先に見てもらう。</t>
+着替えて、髪を整える。この日の流れと、歩いてもらう道を先に見てもらう。</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>この日は店休日なので、一日、店内を使えます。着替えも荷物置き場も店内です。</t>
+          <t>この日は店休日なので、午前中は店内を使えます。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>9:30〜10:05</t>
+          <t>9:30〜10:10</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>店内のレジまわり → 店の前</t>
+          <t>店内 → 店の前</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -738,426 +738,447 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
+          <t>写真撮影（スチール）
+店内の商品と、鞄を持つ姿を静止画で撮る。</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>40分</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>動画より先に写真を済ませます。カメラに慣れる時間にもなります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>10:10〜10:40</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>店内のレジまわり → 店の前</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>難波遥さん、店の人
+商品、鞄</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
           <t>⑤ S6 購入・使う
 1枚目 会計の引き → 2枚目 手渡しと笑顔 → 3枚目 使っている手元。</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>7秒</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>店の人と二人で映るのは、ここだけです。①の一色目のまま撮ります。セリフはありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ①  四 色 を 一 巡 ず つ （ 外 → 店 の 扉 → 店 内 ）</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>店の人と二人で映るのは、ここだけです。買う人の役。セリフはありません。</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>10:05〜10:40</t>
+          <t>10:40〜11:05</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>けやき並木の歩道 → 店の扉 → 店内</t>
+          <t>店内の台（真上から撮れるところ）</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>難波遥さん
+鞄、中に入れる持ち物</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>④ S2 中を見せる
+1枚目 口を開ける（真俯瞰）→ 2枚目 中身を整える手（真俯瞰の寄り）→ 3枚目 横にスライドして次へつなぐ。</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>7秒</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>手が真俯瞰で映ります。鞄に入れる持ち物は、先に並べておきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>11:05〜11:25</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>店の前 ＋ 店内（置き画）</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>難波遥さん
+鞄、持ち物、靴、ロゴ</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>④ S4 立ち止まって終わる
+1枚目 立ち止まる（店の前・固定）→ 2枚目 鞄と持ち物の置き画（店内・真俯瞰）→ 3枚目 ロゴ。</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>8秒</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>靴と持ち物も一緒に並べて撮ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>11:25〜11:45</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>店の前の柵・手すり（けやき並木側）</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>難波遥さん
+鞄、柵</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>④ S1 街に置く
+1枚目 柵に掛ける（引き）→ 2枚目 肩に掛けて立つ（横・引き）→ 3枚目 並木の下・全身。</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>8秒</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>最初と最後は同じ柵。カメラは止めたままで、動くのは背景の街だけです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>11:45〜12:15</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>みゆき通り ／ 根津美術館前の坂（南青山）</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>難波遥さん
+鞄</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>④ S3 街を歩く
+1枚目 通りを歩く（引き）→ 2枚目 肩の鞄に寄る。</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>7秒</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>人の少ない通りで。ここは手持ちで撮ります。顔は主役にしません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>12:15〜13:00</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>昼休み（店舗の近く）</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>45分</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>荷物と衣装は、昼のあいだに車へ積みます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>13:00〜13:30</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>移動（表参道 → 代官山）</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>車で十五分ほど。近くのコインパーキングに停めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 午 後 ── 代 官 山  （ 四 色 を 一 色 ず つ 。 着 替 え は 車 の 中 ）</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>13:30〜14:00</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>旧山手通りのけやき並木（歩道）</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>難波遥さん
 一色目の衣装・鞄</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>① S1 一色目
-1枚目 歩いてくる全身の引き・正面（並木が奥まで抜ける位置）→ 2枚目 同じ位置から腰より上 → 3枚目 扉をまたいで中へ入る → 4枚目 店内を歩く → 5枚目 定位置の立ち姿。</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
+1枚目 全身の引き・正面（並木が奥まで抜ける位置）→ 2枚目 同じ位置から腰より上。街路樹の幹の裏を通った一コマでつなぐ。</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>5秒</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>ここから四回、色を変えます。表情はすまし顔で。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>10:40〜11:15</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>横断歩道（交差点から離れた端） → 店の扉 → 店内</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>ここから四回、色を変えます。表情はすまし顔で。着替えは車の中、十分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>14:00〜14:30</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>ヒルサイドテラス前の歩道（白い壁と列柱を背に）</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>難波遥さん
 二色目の衣装・鞄</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>① S2 二色目
-1枚目 道を渡りきるところの引き → 2枚目 腰より上（サングラスを直す）。扉・店内・定位置は一色目と同じ。</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
+1枚目 引き → 2枚目 膝から上。柱の裏を通った一コマでつなぐ。</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>5秒</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>ここは笑った表情で。着替え十分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>11:15〜11:50</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>並木の木ぎわ → 店の扉 → 店内</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>敷地には入りません。歩道から撮ります。ここは笑った表情で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>14:30〜15:00</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>猿楽町の坂と階段</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>難波遥さん
 三色目の衣装・鞄</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>① S3 三色目
-1枚目 木の後ろを通って歩く引き → 2枚目 腰より上。扉・店内・定位置は同じ。</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
+1枚目 坂を上ってくる引き → 2枚目 腰より上。手すりの前を通った一コマでつなぐ。</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>5秒</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>少し急ぎ足の表情で。着替え十分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>11:50〜12:25</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>店の前 → 店の扉 → 店内</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>少し急ぎ足の表情で。色が変わるごとに、一段ずつ寄っていきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>15:00〜15:30</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>八幡通りの軒下（暗い区間）</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>難波遥さん
 四色目の衣装・鞄</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>① S4 四色目
-1枚目 扉をまたいで中へ入る引き → 2枚目 腰より上（鞄を掛け直して笑う）。店内と定位置も同じ。</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
+1枚目 軒下に入っていく引き → 2枚目 胸から上（鞄を掛け直して笑う）。</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>5秒</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>四色とも同じ立ち位置・同じ画角で撮ります。着替え十分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>12:25〜12:35</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>店内（定位置）</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>四色のなかで、ここがいちばん寄ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>15:30〜15:45</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>代官山駅前の歩道（人通りのあるところ）</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>難波遥さん
 四色ぶんの衣装・鞄</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>① S5 巻き戻る
-店内の通路を歩くところを、色ごとに同じ画角で撮り足す。</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
+1枚目 歩道を歩く（人が横切るたびに一つ前の服に戻る）→ 2枚目 腰より上。</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>7秒</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>四色を並べる最後のカットは、難波さんが帰ったあとに撮ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>12:35〜13:20</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>昼休み（表参道）</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>45分</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>昼休みのあいだに、④の一そろいに着替えます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>13:20〜13:45</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>移動（表参道 → 代官山）</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>25分</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>荷物は持って出ます。撮影は代官山で終わりです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 午 後 ── 代 官 山</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>13:45〜14:05</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>代官山（柵か手すりのあるところ）</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>難波遥さん
-鞄、柵</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>④ S1 街に置く
-1枚目 柵に掛ける（引き）→ 2枚目 肩に掛けて立つ（横・引き）→ 3枚目 街路樹の下・全身。</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>8秒</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>最初と最後は同じ柵。カメラは止めたままで、動くのは背景の街だけです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>14:05〜14:25</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>S1と同じ柵</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>難波遥さん
-鞄、持ち物、靴、ロゴ</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>④ S4 立ち止まって終わる
-1枚目 立ち止まる（固定）→ 2枚目 鞄と持ち物の置き画（真俯瞰）→ 3枚目 ロゴ。</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>8秒</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>靴と持ち物も一緒に並べて撮ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>14:25〜14:50</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>ベンチか石段（真上から撮れるところ）</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>難波遥さん
-鞄、中に入れる持ち物</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>④ S2 中を見せる
-1枚目 口を開ける（真俯瞰）→ 2枚目 中身を整える手（真俯瞰の寄り）→ 3枚目 横にスライドして次へつなぐ。</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>7秒</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>手が真俯瞰で映ります。鞄に入れる持ち物は、先に並べておきます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>14:50〜15:10</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>代官山の裏通り（人がほとんど通らない側）</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>難波遥さん
-鞄</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>④ S3 街を歩く
-1枚目 通りを歩く（引き・固定）→ 2枚目 肩の鞄に寄る。</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>7秒</t>
-        </is>
-      </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>人の少ない裏側で。顔は主役にしません。</t>
+          <t>ここまでで難波さんは終わりです。四色を並べる最後のカットは、難波さんが帰ったあとに店で撮ります。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="A14:F14"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
